--- a/orcamento-marcenaria/tests/arquivos_exemplo/referencias_pendentes_quarto_maria.xlsx
+++ b/orcamento-marcenaria/tests/arquivos_exemplo/referencias_pendentes_quarto_maria.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Referencias Pendentes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pendencias Quarto Maria" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -93,18 +98,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,17 +476,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
@@ -488,650 +494,718 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Referencias PENDENTES - Projeto Quarto Maria</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>Referencias PENDENTES - Projeto Quarto Maria (v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estas sao as 20 referencias do projeto Quarto Maria que ainda NAO tem preco na tabela principal. Descricao, Categoria e Espessura ja vieram preenchidas automaticamente (em preto) a partir do codigo Promob -- confira e corrija se precisar. Preencha em AZUL: Preco Unitario, Fornecedor, Codigo Interno (opcional). Depois eu incorporo essas linhas na tabela principal.</t>
+          <t>Faltam precos para estas referencias completarem o orcamento. SECAO 1 = chapas de MDF (preencha Preco Chapa Fechada e Preco Fita de Borda). SECAO 2 = ferragens/componentes (preencha so Preco Unitario UN). Descricao/Categoria/Espessura ja vieram preenchidas automaticamente (preto) -- preencha em AZUL.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>REFERENCE (codigo Promob)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Codigo Interno</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Descricao do material/acabamento</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Espessura (mm)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Unidade (M2/UN/ML)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Preco Unitario (R$)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Fornecedor</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Data Atualizacao</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Observacoes</t>
+          <t>SECAO 1 - Chapas de MDF (fita do mesmo acabamento)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Codigo Interno</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Descricao</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Espessura (mm)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Preco Chapa Fechada (R$)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Preco Fita de Borda (R$/m)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Fornecedor</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Observacoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>1.0260.18.Branco.MDF</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Moldura Engros</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Chapa MDF</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>1.0854.18.Duratex.Essencial.Rosa Infinito.MDF</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Fechamento Lateral</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Chapa MDF</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>1.1086.000</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Dobradiça Aço s/ Amort. Reta / Baixa</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Ferragem</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>1.1089.450</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Corrediça Telescópica 450</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Ferragem</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2.0109.18.Duratex.Essencial.Rosa Infinito.MDF</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Vista Linear</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>1.1089.500</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Corrediça Telescópica 500</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Ferragem</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2.0160.18.Branco.MDF</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Prateleira Linear de Madeira 18</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2.0095C.734.Branco</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Gaveta Interna c/ Contra Frente</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Componente Montado</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>734</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2.2008.18.Branco.MDF</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Base Linear 18</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2.0109.18.Duratex.Essencial.Rosa Infinito.MDF</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Vista Linear</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2.2008.18.Duratex.Essencial.Rosa Infinito.MDF</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Base Linear 18</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Chapa MDF</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2.0135.30.Duratex.Essencial.Rosa Infinito</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Fechamento p/ Armário</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2.2015.18.Duratex.Essencial.Rosa Infinito.MDF</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Fundo 18</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2.0160.18.Branco.MDF</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Prateleira Linear de Madeira 18</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2.2015.9.Branco.MDF</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Fundo 9</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Chapa MDF</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2.2029.18.Branco.MDF</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Sarrafo Linear Horizontal 18</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2.0295.720.Branco</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Sapateira com contra-frente</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Componente Montado</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>720</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2.1029.000</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Suporte</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Ferragem</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2.2033.18.Branco.MDF</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Lateral 18</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2.2008.18.Branco.MDF</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Base Linear 18</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2.2033.18.Duratex.Essencial.Rosa Infinito.MDF</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Lateral 18</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Chapa MDF</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2.2008.18.Duratex.Essencial.Rosa Infinito.MDF</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Base Linear 18</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2.2035.18.Duratex.Essencial.Rosa Infinito.MDF</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Afastador p/ Montante 18 / Lateral Montante 18</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Chapa MDF</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2.2015.18.Duratex.Essencial.Rosa Infinito.MDF</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Fundo 18</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Chapa MDF</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2.2015.9.Branco.MDF</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Fundo 9</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Chapa MDF</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SECAO 2 - Ferragens / Componentes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2.2029.18.Branco.MDF</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr"/>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Codigo Interno</t>
+        </is>
+      </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Sarrafo Linear Horizontal 18</t>
+          <t>Descricao</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Chapa MDF</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>18</v>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Espessura (mm)</t>
+        </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Preco Unitario UN (R$)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>(nao aplicavel)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Fornecedor</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Observacoes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2.2033.18.Branco.MDF</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Lateral 18</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Chapa MDF</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>1.1086.000</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Dobradiça Aço s/ Amort. Reta / Baixa</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2.2033.18.Duratex.Essencial.Rosa Infinito.MDF</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Lateral 18</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Chapa MDF</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1.1089.450</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Corrediça Telescópica 450</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2.2035.18.Duratex.Essencial.Rosa Infinito.MDF</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Afastador p/ Montante 18 / Lateral Montante 18</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Chapa MDF</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>1.1089.500</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Corrediça Telescópica 500</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2.0095C.734.Branco</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Gaveta Interna c/ Contra Frente</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2.0135.30.Duratex.Essencial.Rosa Infinito</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Fechamento p/ Armário</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2.0295.720.Branco</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Sapateira com contra-frente</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2.1029.000</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Porta Provençal Configurável</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Processo de Fabricação</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Ferragem/Componente</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
